--- a/artfynd/A 53822-2025 artfynd.xlsx
+++ b/artfynd/A 53822-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>115919297</v>
       </c>
       <c r="B2" t="n">
-        <v>56323</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,6 +788,332 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>116444755</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58209</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102980</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ladusvala</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hirundo rustica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Österrå, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>607558</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7022882</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>109008901</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58541</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102987</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sädesärla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Österrå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>607593</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7022807</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>94312734</v>
+      </c>
+      <c r="B5" t="n">
+        <v>41972</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>213797</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Humlerotfjäril</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepialus humuli</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Österrå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>607602</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7022863</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gunilla Viksten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
